--- a/data/trans_orig/P19C04-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P19C04-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por la extracción de algún diente o muela en 2007</t>
+          <t>Población según si el motivo por su última visita al dentista fue por la extracción de algún diente o muela en 2007 (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>191114</t>
+          <t>190569</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>238782</t>
+          <t>238703</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>196204</t>
+          <t>191833</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>244097</t>
+          <t>242784</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>396815</t>
+          <t>396259</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>466579</t>
+          <t>466695</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>450583</t>
+          <t>450662</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>498251</t>
+          <t>498796</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,36%</t>
+          <t>65,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,28%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>714862</t>
+          <t>716175</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>762755</t>
+          <t>767126</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>74,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1181745</t>
+          <t>1181629</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1251509</t>
+          <t>1252065</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>75,96%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>213805</t>
+          <t>211668</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>270349</t>
+          <t>266966</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>136546</t>
+          <t>136780</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>183822</t>
+          <t>183238</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>360806</t>
+          <t>364787</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>432678</t>
+          <t>439060</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,34%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1044099</t>
+          <t>1047482</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1100643</t>
+          <t>1102780</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>79,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1189373</t>
+          <t>1189957</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1236649</t>
+          <t>1236415</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2254965</t>
+          <t>2248583</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2326837</t>
+          <t>2322856</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>86,43%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25505</t>
+          <t>26478</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>50623</t>
+          <t>50849</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16791</t>
+          <t>17048</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36998</t>
+          <t>36754</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>46896</t>
+          <t>48368</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>79408</t>
+          <t>78622</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,15%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>400306</t>
+          <t>400080</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>425424</t>
+          <t>424451</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>371785</t>
+          <t>372029</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>391992</t>
+          <t>391735</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>780304</t>
+          <t>781090</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>812816</t>
+          <t>811344</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,37%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>450878</t>
+          <t>449175</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>531386</t>
+          <t>530224</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>364094</t>
+          <t>368865</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>437561</t>
+          <t>439813</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>834415</t>
+          <t>838333</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>948895</t>
+          <t>946159</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,21%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1923356</t>
+          <t>1924518</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2003864</t>
+          <t>2005567</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,35%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>81,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2303376</t>
+          <t>2301124</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2376843</t>
+          <t>2372072</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4246784</t>
+          <t>4249520</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4361264</t>
+          <t>4357346</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>81,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>83,86%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por la extracción de algún diente o muela en 2012</t>
+          <t>Población según si el motivo por su última visita al dentista fue por la extracción de algún diente o muela en 2012 (tasa de respuesta: 99,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>294393</t>
+          <t>294941</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>351183</t>
+          <t>351186</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>272242</t>
+          <t>270729</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>329800</t>
+          <t>331101</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>580470</t>
+          <t>580232</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>669275</t>
+          <t>666416</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>34,94%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>427991</t>
+          <t>427988</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>484781</t>
+          <t>484233</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>62,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>798406</t>
+          <t>797105</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>855964</t>
+          <t>857477</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>70,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>76,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1238104</t>
+          <t>1240963</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1326909</t>
+          <t>1327147</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,91%</t>
+          <t>65,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,57%</t>
+          <t>69,58%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>320674</t>
+          <t>320112</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>387149</t>
+          <t>387949</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>192103</t>
+          <t>190975</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>247503</t>
+          <t>246094</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>531226</t>
+          <t>524840</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>620495</t>
+          <t>619991</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,92%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1301129</t>
+          <t>1300329</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1367604</t>
+          <t>1368166</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>77,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,01%</t>
+          <t>81,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1341710</t>
+          <t>1343119</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1397110</t>
+          <t>1398238</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2656996</t>
+          <t>2657500</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2746265</t>
+          <t>2752651</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,07%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>83,99%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32571</t>
+          <t>33160</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>61174</t>
+          <t>61285</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23095</t>
+          <t>22588</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>47088</t>
+          <t>47755</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>61380</t>
+          <t>61163</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>99740</t>
+          <t>96587</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,16%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>380960</t>
+          <t>380849</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>409563</t>
+          <t>408974</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>376635</t>
+          <t>375968</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>400628</t>
+          <t>401135</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>766117</t>
+          <t>769270</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>804477</t>
+          <t>804694</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,94%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>671870</t>
+          <t>672222</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>768829</t>
+          <t>767242</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>505517</t>
+          <t>505336</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>595047</t>
+          <t>593276</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1209006</t>
+          <t>1204904</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1339380</t>
+          <t>1337668</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,11%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2140757</t>
+          <t>2142344</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2237716</t>
+          <t>2237364</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>73,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,91%</t>
+          <t>76,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2546095</t>
+          <t>2547866</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2635625</t>
+          <t>2635806</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>81,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4711348</t>
+          <t>4713060</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4841722</t>
+          <t>4845824</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,86%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>80,09%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por la extracción de algún diente o muela en 2016</t>
+          <t>Población según si el motivo por su última visita al dentista fue por la extracción de algún diente o muela en 2016 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>133399</t>
+          <t>132234</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>173138</t>
+          <t>173713</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>117552</t>
+          <t>118384</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>162029</t>
+          <t>161901</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>260470</t>
+          <t>261610</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>321290</t>
+          <t>319962</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,19%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>284281</t>
+          <t>283706</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>324020</t>
+          <t>325185</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>62,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>70,84%</t>
+          <t>71,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>476845</t>
+          <t>476973</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>521322</t>
+          <t>520490</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,64%</t>
+          <t>74,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>81,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>775003</t>
+          <t>776331</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>835823</t>
+          <t>834683</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,69%</t>
+          <t>70,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,24%</t>
+          <t>76,14%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>245629</t>
+          <t>247100</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>308415</t>
+          <t>309980</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>171104</t>
+          <t>168121</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>225800</t>
+          <t>221741</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>433741</t>
+          <t>432136</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>517462</t>
+          <t>510766</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,0%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1388190</t>
+          <t>1386625</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1450976</t>
+          <t>1449505</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>81,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1481824</t>
+          <t>1485883</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1536520</t>
+          <t>1539503</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2886767</t>
+          <t>2893463</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2970488</t>
+          <t>2972093</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>87,31%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30501</t>
+          <t>31829</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>58675</t>
+          <t>59081</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28250</t>
+          <t>27760</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>53298</t>
+          <t>52583</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>65974</t>
+          <t>66888</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>100866</t>
+          <t>101166</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,04%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>440569</t>
+          <t>440163</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>468743</t>
+          <t>467415</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>455022</t>
+          <t>455737</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>480070</t>
+          <t>480560</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>906698</t>
+          <t>906398</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>941590</t>
+          <t>940676</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,36%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>434063</t>
+          <t>433711</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>512854</t>
+          <t>514123</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>337117</t>
+          <t>339029</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>414753</t>
+          <t>412680</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>783047</t>
+          <t>792823</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>896637</t>
+          <t>904652</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,42%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2140415</t>
+          <t>2139146</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2219206</t>
+          <t>2219558</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>80,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2440065</t>
+          <t>2442138</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2517701</t>
+          <t>2515789</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4611450</t>
+          <t>4603435</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4725040</t>
+          <t>4715264</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>85,61%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por la extracción de algún diente o muela en 2023</t>
+          <t>Población según si el motivo por su última visita al dentista fue por la extracción de algún diente o muela en 2023 (tasa de respuesta: 99,53%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>147478</t>
+          <t>146893</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>182958</t>
+          <t>183175</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>153524</t>
+          <t>152704</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>186770</t>
+          <t>186093</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>308017</t>
+          <t>309504</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>355498</t>
+          <t>362136</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>30,05%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>300387</t>
+          <t>300170</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>335867</t>
+          <t>336452</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>62,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,49%</t>
+          <t>69,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>534846</t>
+          <t>535523</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>568092</t>
+          <t>568912</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>74,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>78,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>849463</t>
+          <t>842825</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>896944</t>
+          <t>895457</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>69,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>74,31%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>188357</t>
+          <t>188668</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>315787</t>
+          <t>316331</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>126127</t>
+          <t>125189</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>206587</t>
+          <t>208016</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>361189</t>
+          <t>355446</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>510862</t>
+          <t>506724</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,44%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1914750</t>
+          <t>1914206</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2042180</t>
+          <t>2041869</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>85,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1991319</t>
+          <t>1989890</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2071779</t>
+          <t>2072717</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3917580</t>
+          <t>3921718</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4067253</t>
+          <t>4072996</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,97%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>38746</t>
+          <t>38689</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>68716</t>
+          <t>66931</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22200</t>
+          <t>22985</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41901</t>
+          <t>42133</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>66562</t>
+          <t>66418</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>101460</t>
+          <t>98631</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,69%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>562600</t>
+          <t>564385</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>592570</t>
+          <t>592627</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>609710</t>
+          <t>609478</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>629411</t>
+          <t>628626</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1181467</t>
+          <t>1184296</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1216365</t>
+          <t>1216509</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,82%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>380117</t>
+          <t>380265</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>547821</t>
+          <t>541993</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>305975</t>
+          <t>308413</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>417478</t>
+          <t>415762</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>740069</t>
+          <t>746200</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>936856</t>
+          <t>930891</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,46%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2797376</t>
+          <t>2803204</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2965080</t>
+          <t>2964932</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3153655</t>
+          <t>3155371</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3265158</t>
+          <t>3262720</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5979474</t>
+          <t>5985439</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6176261</t>
+          <t>6170130</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,21%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P19C04-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P19C04-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>190569</t>
+          <t>190023</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>238703</t>
+          <t>236563</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>191833</t>
+          <t>193383</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>242784</t>
+          <t>245687</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>396259</t>
+          <t>396064</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>466695</t>
+          <t>467357</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>28,35%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>450662</t>
+          <t>452802</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>498796</t>
+          <t>499342</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>65,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>72,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>716175</t>
+          <t>713272</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>767126</t>
+          <t>765576</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,68%</t>
+          <t>74,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1181629</t>
+          <t>1180967</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1252065</t>
+          <t>1252260</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,69%</t>
+          <t>71,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>75,97%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>211668</t>
+          <t>212645</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>266966</t>
+          <t>267846</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>136780</t>
+          <t>139175</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>183238</t>
+          <t>186614</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>364787</t>
+          <t>364685</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>439060</t>
+          <t>438369</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,31%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1047482</t>
+          <t>1046602</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1102780</t>
+          <t>1101803</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>79,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>83,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1189957</t>
+          <t>1186581</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1236415</t>
+          <t>1234020</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2248583</t>
+          <t>2249274</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2322856</t>
+          <t>2322958</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>83,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26478</t>
+          <t>26810</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>50849</t>
+          <t>52333</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17048</t>
+          <t>16933</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36754</t>
+          <t>36563</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>48368</t>
+          <t>48086</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>78622</t>
+          <t>79896</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,29%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>400080</t>
+          <t>398596</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>424451</t>
+          <t>424119</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>372029</t>
+          <t>372220</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>391735</t>
+          <t>391850</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>781090</t>
+          <t>779816</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>811344</t>
+          <t>811626</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,41%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>449175</t>
+          <t>452315</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>530224</t>
+          <t>532460</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>368865</t>
+          <t>368079</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>439813</t>
+          <t>443924</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>838333</t>
+          <t>838459</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>946159</t>
+          <t>950149</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,29%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1924518</t>
+          <t>1922282</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2005567</t>
+          <t>2002427</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>78,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>81,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2301124</t>
+          <t>2297013</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2372072</t>
+          <t>2372858</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4249520</t>
+          <t>4245530</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4357346</t>
+          <t>4357220</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>294941</t>
+          <t>295466</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>351186</t>
+          <t>353325</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>45,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>270729</t>
+          <t>269993</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>331101</t>
+          <t>329853</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>580232</t>
+          <t>583694</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>666416</t>
+          <t>664907</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>34,86%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>427988</t>
+          <t>425849</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>484233</t>
+          <t>483708</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>54,93%</t>
+          <t>54,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>62,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>797105</t>
+          <t>798353</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>857477</t>
+          <t>858213</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,65%</t>
+          <t>70,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1240963</t>
+          <t>1242472</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1327147</t>
+          <t>1323685</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>65,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,58%</t>
+          <t>69,4%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>320112</t>
+          <t>321724</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>387949</t>
+          <t>388091</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>190975</t>
+          <t>190561</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>246094</t>
+          <t>244872</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>524840</t>
+          <t>527338</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>619991</t>
+          <t>614140</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,74%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1300329</t>
+          <t>1300187</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1368166</t>
+          <t>1366554</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,02%</t>
+          <t>77,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1343119</t>
+          <t>1344341</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1398238</t>
+          <t>1398652</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2657500</t>
+          <t>2663351</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2752651</t>
+          <t>2750153</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>81,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>83,91%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33160</t>
+          <t>33199</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>61285</t>
+          <t>60783</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22588</t>
+          <t>21815</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>47755</t>
+          <t>45194</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>61163</t>
+          <t>60288</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>96587</t>
+          <t>96853</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,19%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>380849</t>
+          <t>381351</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>408974</t>
+          <t>408935</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>375968</t>
+          <t>378529</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>401135</t>
+          <t>401908</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>769270</t>
+          <t>769004</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>804694</t>
+          <t>805569</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>93,04%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>672222</t>
+          <t>669936</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>767242</t>
+          <t>766627</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>505336</t>
+          <t>507260</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>593276</t>
+          <t>592001</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1204904</t>
+          <t>1207381</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1337668</t>
+          <t>1335356</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,07%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2142344</t>
+          <t>2142959</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2237364</t>
+          <t>2239650</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>73,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2547866</t>
+          <t>2549141</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2635806</t>
+          <t>2633882</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>81,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4713060</t>
+          <t>4715372</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4845824</t>
+          <t>4843347</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>77,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,09%</t>
+          <t>80,05%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>132234</t>
+          <t>132301</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>173713</t>
+          <t>172466</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>118384</t>
+          <t>118378</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>161901</t>
+          <t>162410</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>261610</t>
+          <t>260377</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>319962</t>
+          <t>320388</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,22%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>283706</t>
+          <t>284953</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>325185</t>
+          <t>325118</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,02%</t>
+          <t>62,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>71,09%</t>
+          <t>71,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>476973</t>
+          <t>476464</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>520490</t>
+          <t>520496</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>74,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>776331</t>
+          <t>775905</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>834683</t>
+          <t>835916</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>70,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>76,25%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>247100</t>
+          <t>248437</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>309980</t>
+          <t>308136</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>168121</t>
+          <t>168099</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>221741</t>
+          <t>223884</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>432136</t>
+          <t>427448</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>510766</t>
+          <t>514279</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,11%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1386625</t>
+          <t>1388469</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1449505</t>
+          <t>1448168</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>81,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1485883</t>
+          <t>1483740</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1539503</t>
+          <t>1539525</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>86,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2893463</t>
+          <t>2889950</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2972093</t>
+          <t>2976781</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>87,44%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31829</t>
+          <t>32350</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>59081</t>
+          <t>58129</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27760</t>
+          <t>27456</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>52583</t>
+          <t>52269</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>66888</t>
+          <t>66156</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>101166</t>
+          <t>102120</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,14%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>440163</t>
+          <t>441115</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>467415</t>
+          <t>466894</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>88,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>455737</t>
+          <t>456051</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>480560</t>
+          <t>480864</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>906398</t>
+          <t>905444</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>940676</t>
+          <t>941408</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,43%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>433711</t>
+          <t>432305</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>514123</t>
+          <t>511629</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>339029</t>
+          <t>334851</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>412680</t>
+          <t>413501</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>792823</t>
+          <t>790354</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>904652</t>
+          <t>899902</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,34%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2139146</t>
+          <t>2141640</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2219558</t>
+          <t>2220964</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>80,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2442138</t>
+          <t>2441317</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2515789</t>
+          <t>2519967</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>85,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>88,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4603435</t>
+          <t>4608185</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4715264</t>
+          <t>4717733</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>85,65%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>164796</t>
+          <t>184581</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>146893</t>
+          <t>165155</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>183175</t>
+          <t>206047</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>38,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>169076</t>
+          <t>181440</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>152704</t>
+          <t>164520</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>186093</t>
+          <t>201446</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,17 +5607,17 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>333872</t>
+          <t>366021</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>309504</t>
+          <t>337624</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>362136</t>
+          <t>394461</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>29,87%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>318549</t>
+          <t>351499</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>300170</t>
+          <t>330033</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>336452</t>
+          <t>370925</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>65,91%</t>
+          <t>65,57%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>61,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,61%</t>
+          <t>69,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>552540</t>
+          <t>603152</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>535523</t>
+          <t>583146</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>568912</t>
+          <t>620072</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>76,57%</t>
+          <t>76,87%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,21%</t>
+          <t>74,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,84%</t>
+          <t>79,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,17 +5720,17 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>871089</t>
+          <t>954651</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>842825</t>
+          <t>926211</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>895457</t>
+          <t>983048</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,95%</t>
+          <t>70,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,31%</t>
+          <t>74,44%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>483345</t>
+          <t>536080</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>483345</t>
+          <t>536080</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>483345</t>
+          <t>536080</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>721616</t>
+          <t>784592</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>721616</t>
+          <t>784592</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>721616</t>
+          <t>784592</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1204961</t>
+          <t>1320672</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1204961</t>
+          <t>1320672</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1204961</t>
+          <t>1320672</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,102 +5880,102 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>268600</t>
+          <t>312511</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>188668</t>
+          <t>278407</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>316331</t>
+          <t>350254</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
+          <t>14,56%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>12,97%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>16,32%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>200250</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>176827</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>222924</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>9,49%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>8,38%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>10,56%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>606</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>512761</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>470197</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>553553</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
           <t>12,04%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>8,46%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>14,18%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>296</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>175652</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>125189</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>208016</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>7,99%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>5,7%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>9,46%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>606</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>444252</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>355446</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>506724</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>10,03%</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>13,0%</t>
         </is>
       </c>
     </row>
@@ -5993,102 +5993,102 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1961937</t>
+          <t>1833967</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1914206</t>
+          <t>1796224</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2041869</t>
+          <t>1868071</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
+          <t>85,44%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>83,68%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>87,03%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2553</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1910342</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>1887668</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>1933765</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>90,51%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>89,44%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>91,62%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>4166</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>3744309</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>3703517</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>3786873</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
           <t>87,96%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>85,82%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>91,54%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>2553</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>2022254</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>1989890</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>2072717</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>92,01%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>90,54%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>94,3%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>4166</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>3984190</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>3921718</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>4072996</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>89,97%</t>
-        </is>
-      </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>87,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>88,95%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2230537</t>
+          <t>2146478</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2230537</t>
+          <t>2146478</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2230537</t>
+          <t>2146478</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2197906</t>
+          <t>2110592</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2197906</t>
+          <t>2110592</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2197906</t>
+          <t>2110592</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4428442</t>
+          <t>4257070</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4428442</t>
+          <t>4257070</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4428442</t>
+          <t>4257070</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>50397</t>
+          <t>57532</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>38689</t>
+          <t>44049</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>66931</t>
+          <t>76703</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,67 +6258,67 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>31084</t>
+          <t>34756</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22985</t>
+          <t>25311</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42133</t>
+          <t>46356</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
+          <t>6,4%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>92288</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>76277</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>112632</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
           <t>6,47%</t>
         </is>
       </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>81481</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>66418</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>98631</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>6,35%</t>
-        </is>
-      </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,9%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>580919</t>
+          <t>644309</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>564385</t>
+          <t>625138</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>592627</t>
+          <t>657792</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,67 +6371,67 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>620527</t>
+          <t>689657</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>609478</t>
+          <t>678057</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>628626</t>
+          <t>699102</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
+          <t>93,6%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>96,51%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>1549</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>1333966</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>1313622</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>1349977</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
           <t>93,53%</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>96,47%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>1549</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>1201446</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>1184296</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>1216509</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>93,65%</t>
-        </is>
-      </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,65%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>631316</t>
+          <t>701841</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>631316</t>
+          <t>701841</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>631316</t>
+          <t>701841</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>651611</t>
+          <t>724413</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>651611</t>
+          <t>724413</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>651611</t>
+          <t>724413</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1282927</t>
+          <t>1426254</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1282927</t>
+          <t>1426254</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1282927</t>
+          <t>1426254</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>483793</t>
+          <t>554623</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>380265</t>
+          <t>515844</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>541993</t>
+          <t>598659</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>375812</t>
+          <t>416447</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>308413</t>
+          <t>386214</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>415762</t>
+          <t>451403</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>859605</t>
+          <t>971070</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>746200</t>
+          <t>912108</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>930891</t>
+          <t>1025739</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>14,65%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2861404</t>
+          <t>2829777</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2803204</t>
+          <t>2785741</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2964932</t>
+          <t>2868556</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>83,61%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>82,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3195321</t>
+          <t>3203150</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3155371</t>
+          <t>3168194</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3262720</t>
+          <t>3233383</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>88,49%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6056725</t>
+          <t>6032926</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5985439</t>
+          <t>5978257</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6170130</t>
+          <t>6091888</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>86,98%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3345197</t>
+          <t>3384400</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3345197</t>
+          <t>3384400</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3345197</t>
+          <t>3384400</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3571133</t>
+          <t>3619597</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3571133</t>
+          <t>3619597</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3571133</t>
+          <t>3619597</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>6916330</t>
+          <t>7003996</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>6916330</t>
+          <t>7003996</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>6916330</t>
+          <t>7003996</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
